--- a/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="codes_for_review" sheetId="1" r:id="rId1"/>
-    <sheet name="read_code_mappings" sheetId="2" r:id="rId2"/>
-    <sheet name="icd_code_mappings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J279"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,16 +395,6 @@
           <t>aortic_stenosis</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>aortic_regurgitation</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>mixed_aortic_alve_disease</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -8745,4159 +8733,6 @@
       <c r="F279" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G94"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>standard_concept_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>standard_concept_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>standard_vocabulary_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_id</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_vocabulary_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>313007</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of mitral valve</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>45450432</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Congenital mitral insufficiency</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>P66..00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>313221</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>45513420</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>G120.00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>314054</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>45426832</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[X]Other aortic valve disorders</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gyu5600</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>314054</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>45483534</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Aortic valve disorders</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>G541.00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>314054</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>45510080</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[X]Aortic valve disorders in diseases classified elsewhere</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Gyu5A00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>314054</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>45513434</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aortic valve disorders NOS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>G541z00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>314368</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>45450007</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with incompetence</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>G112.12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>314368</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>45453319</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with regurgitation</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>G112.13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>314368</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>45516821</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>G112.00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>314457</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Congenital stenosis of aortic valve</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>45453737</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Congenital aortic valve stenosis</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P63..00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>315282</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>45436733</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic valve disease NOS</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>G12z.00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>315282</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>45500103</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[X]Other rheumatic aortic valve diseases</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Gyu1100</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>315282</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>45516822</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic valve disease</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>G12..00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>315564</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Aortic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>45436744</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Aortic regurgitation alone, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>G541212</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>315564</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Aortic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>45476938</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aortic incompetence alone, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>G541200</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>315564</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Aortic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>45483535</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Aortic insufficiency alone, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>G541211</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>317890</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mitral and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>45463484</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Mitral and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>G130.00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>318689</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Syphilitic endocarditis of aortic valve</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>45446314</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Syphilitic endocarditis of aortic valve</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>A932200</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>318776</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>45446679</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral insufficiency</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>G111.00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>318776</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>45460018</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mitral regurgitation - rheumatic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>G111.12</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>318776</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>45506678</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Mitral incompetence - rheumatic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>G111.11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>320115</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Mitral insufficiency and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>45433407</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mitral insufficiency and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>G132.00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>320115</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mitral insufficiency and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>45433408</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Mitral regurgitation and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>G132.13</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>320115</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mitral insufficiency and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>45473541</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Mitral incompetence and aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>G132.12</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>320416</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Diseases of mitral and aortic valves</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>45433406</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Diseases of mitral and aortic valves</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>G13..00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>320416</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Diseases of mitral and aortic valves</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>45453320</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Mitral and aortic valve disease NOS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>G13z.00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>320416</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Diseases of mitral and aortic valves</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>45466854</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Multiple mitral and aortic valve involvement</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>G13y.00</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>320429</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis with regurgitation</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>45523363</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>G122.00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>321041</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>45440037</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>G131.14</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>321041</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>45443325</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>G131.00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>321041</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>45493462</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Mitral stenosis and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>G131.13</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>321107</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>45437169</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Congenital aortic valve insufficiency</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>P64..00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>321107</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>45457155</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Congenital aortic valve insufficiency NOS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>P64z.00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>321107</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>45503828</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Congenital aortic valve insufficiency, unspecified</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>P640.00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>439834</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>45463483</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Aortic incompetence - rheumatic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>G121.11</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>439834</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>45510040</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>G121.00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>439834</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>45520054</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Aortic regurgitation - rheumatic</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>G121.12</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>443962</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>45426809</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Mitral valve incompetence</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>G540.00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>443962</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>45453330</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>G540.14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>443962</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>45493469</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>G540.16</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>443962</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>45506689</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Mitral incompetence, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>G540100</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>443962</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>45510049</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Mitral valve insufficiency</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>G540.12</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>4006971</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>45490170</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Tricuspid insufficiency, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>G140400</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>4006971</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>45490171</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>G140412</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>4006971</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>45503417</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Tricuspid regurgitation, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>G140413</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>4012483</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Congenital valvular insufficiency</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>45503830</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of heart valve NEC</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>P6yy.13</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>4035467</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of pulmonary valve</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>45507086</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of the pulmonary valve</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>P60z000</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>4069183</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Subaortic stenosis</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>45490563</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Subaortic stenosis</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>P6y0.00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>4108085</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>45420349</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and regurgitation</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>G14021X</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>4108085</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>45456730</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and incompetence</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>G14021Y</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>4108085</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>45523364</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>G140200</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>4108164</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Aortic valve calcification</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>45513433</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Aortic valve calcification</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>G541700</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>4108235</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Combined disorders of mitral, aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>45523381</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Combined disorders of mitral, aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>G544200</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>4108659</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mitral and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>45433409</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Mitral and aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>G133.12</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>4108659</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Mitral and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>45456728</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Mitral and aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>G133.11</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>4108659</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Mitral and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>45493463</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Mitral and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>G133.00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>4108815</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Non-rheumatic mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>45450014</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Mitral incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>G540000</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>4108819</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Pulmonary valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>45420367</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Pulmonary valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>G543400</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>4109324</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Preductal aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>45480683</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Preductal aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>P711.13</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>4111098</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Aortic stenosis, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>45506690</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Aortic stenosis, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>G541100</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>4111099</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>45483536</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>G541400</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>4111409</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Aortic incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>45426810</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Aortic incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>G541000</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>4111409</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Aortic incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>45443334</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Aortic regurgitation, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>G541012</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>4111409</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Aortic incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>45476937</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Aortic insufficiency, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>G541011</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>4111412</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>45426811</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Tricuspid regurgitation, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>G542012</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>4111412</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>45436745</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Tricuspid insufficiency, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>G542011</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>4111412</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>45473552</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>G542000</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>4111414</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Non-rheumatic tricuspid valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>45470293</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Nonrheumatic tricuspid valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>G542200</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>4111416</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Pulmonary incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>45436746</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Pulmonary regurgitation, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>G543012</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>4111416</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Pulmonary incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>45460035</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Pulmonary insufficiency, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>G543011</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>4111416</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Pulmonary incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>45513435</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Pulmonary incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>G543000</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>4111565</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Disorders of both aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>45453333</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Disorders of both aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>G544000</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>4112093</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Abnormal number of aortic valve cusps</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>45520476</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Fusion of tricuspid valve cusps NEC</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>P6yyD11</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>4113295</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Postductal aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>45423931</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Postductal aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>P712.13</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>4143607</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Rheumatic pulmonary valve insufficiency</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>45500063</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Rheumatic pulmonary insufficiency</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>G141100</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>4147787</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Supravalvar aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>45480686</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Supra-valvular aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>P722400</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>4147787</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supravalvar aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>45483970</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Congenital stenosis of ascending aorta</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>P722411</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>4189343</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>45453331</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Aortic stenosis alone, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>G541300</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>4189343</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>45463496</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>G541500</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>4195677</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>45440038</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence - rheumatic</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>G140112</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>4195677</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>45456729</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Tricuspid regurgitation - rheumatic</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>G140111</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>4195677</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D83">
-        <v>45480258</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid insufficiency</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>G140100</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>4195690</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Aortic valve sclerosis</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D84">
-        <v>45503434</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Aortic valve sclerosis</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>G541600</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>4218450</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Bicuspid aortic valve</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D85">
-        <v>45440453</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Bicuspid aortic valve</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>P641.00</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>4230774</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Heart valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>45490182</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Incompetence of unspecified heart valve</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>G54z000</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>4230774</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Heart valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>45490183</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Regurgitation of unspecified heart valve</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>G54z013</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>4230774</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Heart valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>45513436</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Insufficiency of unspecified heart valve</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>G54z014</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>4237202</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Pulmonic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D89">
-        <v>45443336</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Pulmonary insufficiency, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>G543213</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90">
-        <v>4237202</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Pulmonic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D90">
-        <v>45500075</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Pulmonary regurgitation, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>G543215</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91">
-        <v>4237202</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Pulmonic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D91">
-        <v>45516832</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Pulmonary incompetence, cause unspecified</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>G543200</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92">
-        <v>4244173</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Congenital hypoplasia of aortic valve</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D92">
-        <v>45473965</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Hypoplastic aortic orifice or valve</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>P6yy.11</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93">
-        <v>4246951</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Congenital stenosis of aortic arch</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D93">
-        <v>45460437</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Stenosis of aortic arch</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>P713.11</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94">
-        <v>4312621</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Rheumatic pulmonary valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D94">
-        <v>45430130</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Rheumatic pulmonary stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>G141200</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>standard_concept_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>standard_concept_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>standard_vocabulary_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_id</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_concept_code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>non_standard_vocabulary_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>259123</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Congenital subaortic stenosis</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>45548889</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Congenital subaortic stenosis</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Q24.4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>313007</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of mitral valve</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>45572955</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Congenital mitral insufficiency</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Q23.3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>313221</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>45576862</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>I06.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>314054</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>45548018</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Aortic valve disorders in diseases classified elsewhere</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>I39.1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>314054</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>45581772</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Other aortic valve disorders</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>I35.8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>314054</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>45596201</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aortic valve disorder, unspecified</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>I35.9</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>314457</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Congenital stenosis of aortic valve</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>45587449</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Congenital stenosis of aortic valve</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Q23.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>315282</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>45562335</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Other rheumatic aortic valve diseases</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>I06.8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>315282</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>45567161</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic valve diseases</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>I06</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>315282</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of aortic valve</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>45601019</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic valve disease, unspecified</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>I06.9</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>315564</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aortic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>45572087</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Aortic (valve) insufficiency</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>I35.1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>318776</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral regurgitation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>45552777</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral insufficiency</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>I05.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>320429</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis with regurgitation</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>45572074</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>I06.2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>321107</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>45582641</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Q23.1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>439834</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>45581763</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>I06.1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>443962</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>45601031</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Mitral (valve) insufficiency</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>I34.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>4006971</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tricuspid valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>45601020</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Tricuspid insufficiency</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>I07.1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>4035467</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of pulmonary valve</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>45592364</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Congenital pulmonary valve insufficiency</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Q22.2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>4040820</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rheumatic disease of mitral AND aortic valves</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>45552778</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Disorders of both mitral and aortic valves</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>I08.0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>4108085</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rheumatic tricuspid stenosis and insufficiency</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>45562336</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Tricuspid stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>I07.2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>4108235</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Combined disorders of mitral, aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>45552779</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Combined disorders of mitral, aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>I08.3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>4108819</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Pulmonary valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>45538379</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Pulmonary valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>I37.2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>4111099</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>45562346</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Aortic (valve) stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>I35.2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>4111412</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tricuspid incompetence, non-rheumatic</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>45576870</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Nonrheumatic tricuspid (valve) insufficiency</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>I36.1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>4111414</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Non-rheumatic tricuspid valve stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>45567174</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Nonrheumatic tricuspid (valve) stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>I36.2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>4111565</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Disorders of both aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>45601021</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Disorders of both aortic and tricuspid valves</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>I08.2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>4147787</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supravalvar aortic stenosis</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>45534370</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Stenosis of aorta</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Q25.3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>4189343</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Aortic valve stenosis</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>45576869</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Aortic (valve) stenosis</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>I35.0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>4237202</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Pulmonic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>45576871</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Pulmonary valve insufficiency</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>I37.1</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ICD10</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>4301373</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Rheumatic mitral stenosis with regurgitation</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>45581762</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mitral stenosis with insufficiency</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>I05.2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ICD10</t>
         </is>
       </c>
     </row>

--- a/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:K289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,12 +387,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>aortic_valve_disease_broad</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>aortic_stenosis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>aortic_endocarditis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>aortic_insufficiency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>aortic_valve_disease</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>aortic_stenosis</t>
         </is>
       </c>
     </row>
@@ -425,6 +440,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -455,6 +485,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -485,6 +530,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -515,6 +575,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -545,6 +620,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -575,6 +665,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -605,6 +710,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -635,6 +755,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -665,6 +800,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -672,7 +822,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -693,6 +843,21 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -725,6 +890,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -755,6 +935,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -785,6 +980,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -815,6 +1025,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -845,6 +1070,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -852,7 +1092,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -873,6 +1113,21 @@
       <c r="F17" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -882,7 +1137,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>In synonyms</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -903,6 +1158,21 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -935,6 +1205,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -965,6 +1250,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -995,6 +1295,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1025,6 +1340,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1055,6 +1385,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1085,6 +1430,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1115,6 +1475,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1145,6 +1520,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1175,6 +1565,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1205,6 +1610,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1235,6 +1655,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1265,6 +1700,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1295,6 +1745,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1325,6 +1790,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1355,6 +1835,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1385,6 +1880,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1415,6 +1925,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1445,6 +1970,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1475,6 +2015,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1505,6 +2060,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1535,6 +2105,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1565,6 +2150,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1595,6 +2195,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1625,6 +2240,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1655,6 +2285,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1685,6 +2330,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1715,6 +2375,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1745,6 +2420,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1775,6 +2465,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1805,6 +2510,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1835,6 +2555,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1865,6 +2600,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1895,6 +2645,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1925,6 +2690,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1955,6 +2735,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1985,6 +2780,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -2015,6 +2825,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -2045,6 +2870,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -2075,6 +2915,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -2105,6 +2960,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -2135,6 +3005,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -2165,6 +3050,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -2195,6 +3095,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2225,6 +3140,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2255,6 +3185,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -2285,6 +3230,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -2315,6 +3275,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -2345,6 +3320,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -2375,6 +3365,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -2405,6 +3410,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -2435,6 +3455,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -2465,6 +3500,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -2495,6 +3545,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -2525,6 +3590,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -2555,6 +3635,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -2585,6 +3680,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -2615,6 +3725,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -2622,7 +3747,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>In synonyms</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2643,6 +3768,21 @@
       <c r="F76" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2675,6 +3815,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -2705,6 +3860,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -2735,6 +3905,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -2765,6 +3950,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -2795,6 +3995,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -2825,6 +4040,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -2855,6 +4085,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -2885,6 +4130,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -2915,6 +4175,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -2945,6 +4220,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -2975,6 +4265,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -3005,6 +4310,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -3035,6 +4355,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -3065,6 +4400,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -3095,6 +4445,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -3125,6 +4490,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -3155,6 +4535,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -3185,6 +4580,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -3215,6 +4625,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -3245,6 +4670,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -3275,6 +4715,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -3305,6 +4760,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -3335,6 +4805,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -3365,6 +4850,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -3395,6 +4895,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -3425,6 +4940,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -3455,6 +4985,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -3485,6 +5030,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -3515,6 +5075,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -3545,6 +5120,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -3575,6 +5165,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -3605,6 +5210,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -3635,6 +5255,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -3665,6 +5300,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -3695,6 +5345,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -3725,6 +5390,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -3755,6 +5435,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -3785,6 +5480,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -3815,6 +5525,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -3845,6 +5570,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -3875,6 +5615,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -3905,6 +5660,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -3935,6 +5705,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -3965,6 +5750,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -3995,6 +5795,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -4025,6 +5840,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -4055,6 +5885,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -4085,6 +5930,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -4115,6 +5975,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -4145,6 +6020,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -4175,6 +6065,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -4205,6 +6110,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -4235,6 +6155,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -4265,6 +6200,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -4295,6 +6245,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -4325,6 +6290,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -4355,6 +6335,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -4385,6 +6380,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -4415,6 +6425,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -4445,6 +6470,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -4475,6 +6515,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -4505,6 +6560,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -4535,6 +6605,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -4565,6 +6650,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -4595,6 +6695,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -4625,6 +6740,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -4655,6 +6785,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -4685,6 +6830,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -4715,6 +6875,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -4745,6 +6920,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -4775,6 +6965,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -4805,6 +7010,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -4835,6 +7055,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -4865,6 +7100,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -4895,6 +7145,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -4925,6 +7190,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -4955,6 +7235,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -4985,6 +7280,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -5015,6 +7325,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -5045,6 +7370,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -5075,6 +7415,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -5105,6 +7460,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -5135,6 +7505,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -5165,6 +7550,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -5195,6 +7595,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -5225,6 +7640,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -5232,7 +7662,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>In synonyms</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5253,6 +7683,21 @@
       <c r="F163" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -5285,6 +7730,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -5315,6 +7775,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -5345,6 +7820,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -5375,6 +7865,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -5405,6 +7910,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -5435,6 +7955,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -5465,6 +8000,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -5495,6 +8045,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -5525,6 +8090,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -5555,6 +8135,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -5585,6 +8180,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -5615,6 +8225,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -5645,6 +8270,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -5675,6 +8315,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -5705,6 +8360,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -5735,6 +8405,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -5765,6 +8450,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -5795,6 +8495,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -5825,6 +8540,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -5855,6 +8585,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -5885,6 +8630,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -5915,6 +8675,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -5945,6 +8720,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -5975,6 +8765,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -6005,6 +8810,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -6035,6 +8855,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -6065,6 +8900,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -6095,6 +8945,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -6125,6 +8990,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -6155,6 +9035,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -6185,6 +9080,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -6215,6 +9125,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -6245,6 +9170,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -6275,6 +9215,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -6305,6 +9260,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -6335,6 +9305,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -6365,6 +9350,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -6395,6 +9395,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -6425,6 +9440,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -6455,6 +9485,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -6485,6 +9530,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -6515,6 +9575,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -6545,6 +9620,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -6575,6 +9665,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -6605,6 +9710,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -6635,6 +9755,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -6665,6 +9800,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -6695,6 +9845,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -6725,6 +9890,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -6755,6 +9935,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -6762,7 +9957,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6783,6 +9978,21 @@
       <c r="F214" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6815,6 +10025,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -6822,7 +10047,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6843,6 +10068,21 @@
       <c r="F216" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6875,6 +10115,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -6905,6 +10160,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -6912,7 +10182,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6933,6 +10203,21 @@
       <c r="F219" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6965,6 +10250,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -6995,6 +10295,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -7025,6 +10340,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -7055,6 +10385,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -7085,6 +10430,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -7115,6 +10475,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -7145,6 +10520,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -7175,6 +10565,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -7205,6 +10610,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -7212,7 +10632,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7233,6 +10653,21 @@
       <c r="F229" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7265,6 +10700,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -7295,6 +10745,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -7325,6 +10790,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -7355,6 +10835,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -7385,6 +10880,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -7415,6 +10925,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -7445,6 +10970,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -7475,6 +11015,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -7505,6 +11060,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -7535,6 +11105,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -7565,6 +11150,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -7595,6 +11195,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -7625,6 +11240,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -7655,6 +11285,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -7685,6 +11330,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -7715,6 +11375,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -7745,6 +11420,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -7775,6 +11465,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -7805,6 +11510,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -7835,6 +11555,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -7865,6 +11600,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -7895,6 +11645,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -7925,6 +11690,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -7955,6 +11735,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -7985,6 +11780,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -8015,6 +11825,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -8045,6 +11870,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -8052,7 +11892,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8073,6 +11913,21 @@
       <c r="F257" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8105,6 +11960,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -8135,6 +12005,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -8165,6 +12050,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -8195,6 +12095,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -8225,6 +12140,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -8255,6 +12185,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -8285,6 +12230,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -8315,6 +12275,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266">
@@ -8345,6 +12320,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -8375,6 +12365,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -8405,6 +12410,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -8435,6 +12455,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -8465,6 +12500,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -8495,6 +12545,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -8525,6 +12590,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -8555,6 +12635,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -8585,6 +12680,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -8615,6 +12725,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -8645,6 +12770,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -8675,6 +12815,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -8705,6 +12860,21 @@
           <t>S</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -8733,6 +12903,471 @@
       <c r="F279" t="inlineStr">
         <is>
           <t>S</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>318689</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Syphilitic endocarditis of aortic valve</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>321107</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Congenital insufficiency of aortic valve</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>439834</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Rheumatic aortic regurgitation</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>4108659</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Mitral and aortic incompetence</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>35622773</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Laubry Pezzi syndrome</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>42539157</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Endocarditis of neoaortic valve</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>42597024</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Endocarditis of aortic valve</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>SNOMED Veterinary</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>42599746</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Physiologic aortic insufficiency</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>SNOMED Veterinary</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>43020882</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Infective endocarditis of aortic valve</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>45766095</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>From descendants</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Endocarditis of prosthetic aortic valve</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>SNOMED</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>

--- a/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
+++ b/diagnostics_code/aortic_valve_disease_codes_for_review.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,7 +387,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>aortic_valve_disease_broad</t>
+          <t>aortic_valve_disease</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -403,11 +403,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>aortic_insufficiency</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>aortic_valve_disease</t>
         </is>
       </c>
     </row>
@@ -440,21 +435,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -485,21 +465,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -530,21 +495,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -575,21 +525,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -620,21 +555,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -665,21 +585,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -710,21 +615,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -755,21 +645,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -800,21 +675,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -845,21 +705,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -890,21 +735,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -935,21 +765,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -980,21 +795,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1025,21 +825,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1070,21 +855,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1115,21 +885,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1137,7 +892,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>In synonyms</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1158,21 +913,6 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>T</t>
         </is>
       </c>
     </row>
@@ -1205,21 +945,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1250,21 +975,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1295,21 +1005,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1340,21 +1035,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1385,21 +1065,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1430,21 +1095,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1475,21 +1125,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1520,21 +1155,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1565,21 +1185,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1610,21 +1215,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1655,21 +1245,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1700,21 +1275,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1745,21 +1305,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1790,21 +1335,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1835,21 +1365,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1880,21 +1395,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1925,21 +1425,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1970,21 +1455,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -2015,21 +1485,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -2060,21 +1515,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -2105,21 +1545,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2150,21 +1575,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2195,21 +1605,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -2240,21 +1635,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2285,21 +1665,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2330,21 +1695,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2375,21 +1725,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2420,21 +1755,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -2465,21 +1785,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -2510,21 +1815,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2555,21 +1845,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2600,21 +1875,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -2645,21 +1905,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -2690,21 +1935,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -2735,21 +1965,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -2780,21 +1995,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -2825,21 +2025,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -2870,21 +2055,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -2915,21 +2085,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -2960,21 +2115,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -3005,21 +2145,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -3050,21 +2175,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -3095,21 +2205,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -3140,21 +2235,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -3185,21 +2265,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3230,21 +2295,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -3275,21 +2325,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -3320,21 +2355,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -3365,21 +2385,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -3410,21 +2415,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -3455,21 +2445,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -3500,21 +2475,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -3545,21 +2505,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -3590,21 +2535,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -3635,21 +2565,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -3680,21 +2595,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -3702,7 +2602,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3723,21 +2623,6 @@
       <c r="F75" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
@@ -3770,21 +2655,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -3815,21 +2685,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -3860,21 +2715,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -3905,21 +2745,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -3950,21 +2775,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -3995,21 +2805,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -4040,21 +2835,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -4085,21 +2865,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -4130,21 +2895,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -4175,21 +2925,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -4220,21 +2955,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -4265,21 +2985,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -4310,21 +3015,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -4355,21 +3045,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -4400,21 +3075,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -4445,21 +3105,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -4490,21 +3135,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -4535,21 +3165,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -4580,21 +3195,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -4625,21 +3225,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -4670,21 +3255,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -4715,21 +3285,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -4760,21 +3315,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -4805,21 +3345,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -4850,21 +3375,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -4895,21 +3405,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -4940,21 +3435,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -4985,21 +3465,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -5007,7 +3472,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5028,21 +3493,6 @@
       <c r="F104" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
@@ -5075,21 +3525,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -5120,21 +3555,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -5165,21 +3585,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -5210,21 +3615,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -5255,21 +3645,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -5300,21 +3675,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -5345,21 +3705,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -5390,21 +3735,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -5435,21 +3765,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -5480,21 +3795,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -5525,21 +3825,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -5570,21 +3855,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -5615,21 +3885,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -5660,21 +3915,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -5705,21 +3945,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -5750,21 +3975,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -5795,21 +4005,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -5840,21 +4035,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -5885,21 +4065,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -5930,21 +4095,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -5975,21 +4125,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -6020,21 +4155,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -6042,7 +4162,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>In synonyms</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6063,21 +4183,6 @@
       <c r="F127" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
@@ -6110,21 +4215,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -6155,21 +4245,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -6200,21 +4275,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -6245,21 +4305,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -6290,21 +4335,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -6335,21 +4365,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -6380,21 +4395,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -6425,21 +4425,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -6470,21 +4455,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -6515,21 +4485,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -6560,21 +4515,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -6605,21 +4545,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -6650,21 +4575,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -6695,21 +4605,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -6740,21 +4635,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -6785,21 +4665,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -6830,21 +4695,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -6875,21 +4725,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -6920,21 +4755,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -6965,21 +4785,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -7010,21 +4815,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -7055,21 +4845,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -7100,21 +4875,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -7145,21 +4905,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -7190,21 +4935,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -7235,21 +4965,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -7280,21 +4995,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -7325,21 +5025,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -7347,7 +5032,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7368,21 +5053,6 @@
       <c r="F156" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
@@ -7415,21 +5085,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -7460,21 +5115,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -7505,21 +5145,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -7550,21 +5175,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -7595,21 +5205,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -7640,21 +5235,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -7685,21 +5265,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -7730,21 +5295,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -7775,21 +5325,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -7820,21 +5355,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -7865,21 +5385,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -7910,21 +5415,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -7955,21 +5445,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -8000,21 +5475,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -8045,21 +5505,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -8090,21 +5535,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -8135,21 +5565,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -8180,21 +5595,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -8225,21 +5625,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -8270,21 +5655,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -8315,21 +5685,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -8360,21 +5715,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -8405,21 +5745,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -8450,21 +5775,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -8495,21 +5805,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -8540,21 +5835,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -8585,21 +5865,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -8630,21 +5895,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -8675,21 +5925,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -8720,21 +5955,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -8765,21 +5985,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -8810,21 +6015,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -8855,21 +6045,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -8900,21 +6075,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -8945,21 +6105,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -8990,21 +6135,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -9035,21 +6165,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -9080,21 +6195,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -9125,21 +6225,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -9170,21 +6255,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -9215,21 +6285,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -9260,21 +6315,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -9305,21 +6345,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -9350,21 +6375,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -9395,21 +6405,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -9440,21 +6435,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -9485,21 +6465,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -9530,21 +6495,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -9575,21 +6525,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -9620,21 +6555,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -9665,21 +6585,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -9710,21 +6615,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -9755,21 +6645,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -9800,21 +6675,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -9845,21 +6705,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -9890,21 +6735,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -9935,21 +6765,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -9980,25 +6795,10 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>42595751</v>
+        <v>43020504</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -10007,7 +6807,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Subvalvular fibrous band stenosis</t>
+          <t>Shone complex</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10017,42 +6817,27 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>42597024</v>
+        <v>43020626</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Endocarditis of aortic valve</t>
+          <t>Obstruction of aortic valve due to neoplasm</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10062,33 +6847,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>42597038</v>
+        <v>43020627</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -10097,7 +6867,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Rupture of aortic root</t>
+          <t>Thrombosis of aortic valve</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10107,42 +6877,27 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>42599737</v>
+        <v>43020628</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Congenital valvular aortic stenosis</t>
+          <t>Disruption of aortic valve annulus</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10152,42 +6907,27 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>42599746</v>
+        <v>43020629</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Physiologic aortic insufficiency</t>
+          <t>Dehiscence of aortic valve annulus as complication of procedure</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10197,33 +6937,18 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>42599749</v>
+        <v>43020630</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -10232,7 +6957,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Physiologic mitral insufficiency</t>
+          <t>Disorder of aortic valve prosthesis</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10242,33 +6967,18 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>42599750</v>
+        <v>43020882</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -10277,7 +6987,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Diastolic tricuspid valve regurgitation</t>
+          <t>Infective endocarditis of aortic valve</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10287,33 +6997,18 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>42599795</v>
+        <v>43020903</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -10322,7 +7017,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Mitral valve regurgitation during diastole</t>
+          <t>Subneoaortic valve stenosis</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10332,42 +7027,27 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>SNOMED Veterinary</t>
+          <t>SNOMED</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>43020504</v>
+        <v>43020913</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Shone complex</t>
+          <t>Subaortic stenosis as complication of procedure</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10383,36 +7063,21 @@
       <c r="F223" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>43020626</v>
+        <v>43020914</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Obstruction of aortic valve due to neoplasm</t>
+          <t>Acquired subaortic stenosis associated with functionally univentricular heart</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10428,36 +7093,21 @@
       <c r="F224" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>43020627</v>
+        <v>43020915</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Thrombosis of aortic valve</t>
+          <t>Acquired subaortic stenosis due to restrictive ventricular septal defect associated with functionally univentricular heart</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10473,36 +7123,21 @@
       <c r="F225" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>43020628</v>
+        <v>43020916</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Disruption of aortic valve annulus</t>
+          <t>Congenital subaortic stenosis due to restrictive ventricular septal defect associated with functionally univentricular heart</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10518,36 +7153,21 @@
       <c r="F226" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>43020629</v>
+        <v>43020917</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Dehiscence of aortic valve annulus as complication of procedure</t>
+          <t>Subaortic stenosis associated with functionally univentricular heart as complication of procedure</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10563,36 +7183,21 @@
       <c r="F227" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>43020630</v>
+        <v>43020957</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Disorder of aortic valve prosthesis</t>
+          <t>Regurgitation of fetal pulmonary valve</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10608,27 +7213,12 @@
       <c r="F228" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>43020882</v>
+        <v>43020959</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -10637,7 +7227,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Infective endocarditis of aortic valve</t>
+          <t>Stenosis of fetal aortic valve</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10653,27 +7243,12 @@
       <c r="F229" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>43020903</v>
+        <v>43020960</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -10682,7 +7257,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Subneoaortic valve stenosis</t>
+          <t>Regurgitation of fetal right atrioventricular (not morphologically tricuspid) valve</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10698,27 +7273,12 @@
       <c r="F230" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>43020913</v>
+        <v>43020962</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -10727,7 +7287,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Subaortic stenosis as complication of procedure</t>
+          <t>Regurgitation of fetal left atrioventricular (not morphologically mitral) valve</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10743,27 +7303,12 @@
       <c r="F231" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>43020914</v>
+        <v>43020964</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -10772,7 +7317,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Acquired subaortic stenosis associated with functionally univentricular heart</t>
+          <t>Regurgitation of fetal common atrioventricular valve</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10788,27 +7333,12 @@
       <c r="F232" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>43020915</v>
+        <v>43021070</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -10817,7 +7347,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Acquired subaortic stenosis due to restrictive ventricular septal defect associated with functionally univentricular heart</t>
+          <t>Regurgitation of fetal truncal valve</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10833,36 +7363,21 @@
       <c r="F233" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>43020916</v>
+        <v>43021708</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Congenital subaortic stenosis due to restrictive ventricular septal defect associated with functionally univentricular heart</t>
+          <t>Calcification of aortic valve annulus</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -10878,27 +7393,12 @@
       <c r="F234" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>43020917</v>
+        <v>43021806</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -10907,7 +7407,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Subaortic stenosis associated with functionally univentricular heart as complication of procedure</t>
+          <t>Regurgitation of atrioventricular (not morphologically mitral or tricuspid) valve</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10923,27 +7423,12 @@
       <c r="F235" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>43020957</v>
+        <v>43021943</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -10952,7 +7437,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal pulmonary valve</t>
+          <t>Regurgitation of fetal tricuspid valve</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10968,27 +7453,12 @@
       <c r="F236" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>43020959</v>
+        <v>43021944</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -10997,7 +7467,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Stenosis of fetal aortic valve</t>
+          <t>Regurgitation of fetal mitral valve</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11013,27 +7483,12 @@
       <c r="F237" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>43020960</v>
+        <v>43021945</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -11042,7 +7497,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal right atrioventricular (not morphologically tricuspid) valve</t>
+          <t>Regurgitation of fetal aortic valve</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11058,36 +7513,21 @@
       <c r="F238" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>43020962</v>
+        <v>45757096</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal left atrioventricular (not morphologically mitral) valve</t>
+          <t>Aortic valve disorder in mother complicating childbirth</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11103,27 +7543,12 @@
       <c r="F239" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>43020964</v>
+        <v>45766079</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -11132,7 +7557,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal common atrioventricular valve</t>
+          <t>Prosthetic mitral valve stenosis and regurgitation</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11148,27 +7573,12 @@
       <c r="F240" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>43021070</v>
+        <v>45766080</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -11177,7 +7587,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal truncal valve</t>
+          <t>Acute prosthetic aortic valve regurgitation</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11193,36 +7603,21 @@
       <c r="F241" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>43021708</v>
+        <v>45766081</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Calcification of aortic valve annulus</t>
+          <t>Prosthetic aortic valve stenosis</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11238,36 +7633,21 @@
       <c r="F242" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>43021806</v>
+        <v>45766082</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Regurgitation of atrioventricular (not morphologically mitral or tricuspid) valve</t>
+          <t>Prosthetic aortic valve failure</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11283,36 +7663,21 @@
       <c r="F243" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>43021943</v>
+        <v>45766083</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal tricuspid valve</t>
+          <t>Prosthetic aortic valve failure requiring revision</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11328,27 +7693,12 @@
       <c r="F244" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>43021944</v>
+        <v>45766084</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -11357,7 +7707,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal mitral valve</t>
+          <t>Acute prosthetic mitral valve regurgitation</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11373,27 +7723,12 @@
       <c r="F245" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>43021945</v>
+        <v>45766087</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -11402,7 +7737,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Regurgitation of fetal aortic valve</t>
+          <t>Non-rheumatic pulmonary valve stenosis with regurgitation</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11418,36 +7753,21 @@
       <c r="F246" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>45757096</v>
+        <v>45766089</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Aortic valve disorder in mother complicating childbirth</t>
+          <t>Postprocedural pulmonary valve regurgitation</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11463,27 +7783,12 @@
       <c r="F247" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>45766079</v>
+        <v>45766092</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -11492,7 +7797,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Prosthetic mitral valve stenosis and regurgitation</t>
+          <t>Neopulmonary valve regurgitation</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11508,27 +7813,12 @@
       <c r="F248" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>45766080</v>
+        <v>45766095</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -11537,7 +7827,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Acute prosthetic aortic valve regurgitation</t>
+          <t>Endocarditis of prosthetic aortic valve</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11553,27 +7843,12 @@
       <c r="F249" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>45766081</v>
+        <v>45766099</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -11582,7 +7857,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Prosthetic aortic valve stenosis</t>
+          <t>Postprocedural regurgitation of tricuspid valve</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11598,36 +7873,21 @@
       <c r="F250" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>45766082</v>
+        <v>45766124</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Prosthetic aortic valve failure</t>
+          <t>Postprocedural aortic valve regurgitation</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11643,36 +7903,21 @@
       <c r="F251" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>45766083</v>
+        <v>45766125</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Prosthetic aortic valve failure requiring revision</t>
+          <t>Postprocedural aortic valve stenosis</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11688,27 +7933,12 @@
       <c r="F252" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>45766084</v>
+        <v>45766126</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -11717,7 +7947,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Acute prosthetic mitral valve regurgitation</t>
+          <t>Postprocedural mitral valve regurgitation</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11733,27 +7963,12 @@
       <c r="F253" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>45766087</v>
+        <v>45766136</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -11762,7 +7977,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Non-rheumatic pulmonary valve stenosis with regurgitation</t>
+          <t>Non-rheumatic aortic valve stenosis with regurgitation</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -11778,27 +7993,12 @@
       <c r="F254" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>45766089</v>
+        <v>45766181</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -11807,7 +8007,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Postprocedural pulmonary valve regurgitation</t>
+          <t>Prosthetic tricuspid valve regurgitation</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -11823,27 +8023,12 @@
       <c r="F255" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>45766092</v>
+        <v>45766182</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -11852,7 +8037,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Neopulmonary valve regurgitation</t>
+          <t>Prosthetic pulmonary valve regurgitation</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -11868,27 +8053,12 @@
       <c r="F256" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>45766095</v>
+        <v>45766185</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -11897,7 +8067,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Endocarditis of prosthetic aortic valve</t>
+          <t>Acute prosthetic tricuspid valve regurgitation</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11913,27 +8083,12 @@
       <c r="F257" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>45766099</v>
+        <v>45766186</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -11942,7 +8097,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Postprocedural regurgitation of tricuspid valve</t>
+          <t>Prosthetic aortic valve stenosis and regurgitation</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -11958,27 +8113,12 @@
       <c r="F258" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>45766124</v>
+        <v>45766205</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -11987,7 +8127,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Postprocedural aortic valve regurgitation</t>
+          <t>Neoaortic valve stenosis</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12003,36 +8143,21 @@
       <c r="F259" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>45766125</v>
+        <v>45766206</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Postprocedural aortic valve stenosis</t>
+          <t>Tricuspid valve stenosis with insufficiency</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12048,27 +8173,12 @@
       <c r="F260" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>45766126</v>
+        <v>45766207</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -12077,7 +8187,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Postprocedural mitral valve regurgitation</t>
+          <t>Non-rheumatic mitral valve stenosis with regurgitation</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12093,27 +8203,12 @@
       <c r="F261" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262">
-        <v>45766136</v>
+        <v>45766210</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -12122,7 +8217,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Non-rheumatic aortic valve stenosis with regurgitation</t>
+          <t>Aortic valve regurgitation due to trauma</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12138,27 +8233,12 @@
       <c r="F262" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>T</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>45766181</v>
+        <v>45766211</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -12167,7 +8247,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Prosthetic tricuspid valve regurgitation</t>
+          <t>Aortic valve regurgitation due to dissection</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12183,27 +8263,12 @@
       <c r="F263" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>45766182</v>
+        <v>45766213</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -12212,7 +8277,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Prosthetic pulmonary valve regurgitation</t>
+          <t>Mitral valve regurgitation due to infiltrative disease</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12228,27 +8293,12 @@
       <c r="F264" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>45766185</v>
+        <v>45766214</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -12257,7 +8307,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Acute prosthetic tricuspid valve regurgitation</t>
+          <t>Mitral valve regurgitation due to acute myocardial infarction without papillary muscle and chordal rupture</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12273,36 +8323,21 @@
       <c r="F265" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>45766186</v>
+        <v>45771317</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>From initial search</t>
+          <t>From descendants</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Prosthetic aortic valve stenosis and regurgitation</t>
+          <t>Prosthetic aortic valve failure requiring replacement</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12318,27 +8353,12 @@
       <c r="F266" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>T</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>45766205</v>
+        <v>45771321</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -12347,7 +8367,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Neoaortic valve stenosis</t>
+          <t>Neoaortic valve regurgitation</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12363,36 +8383,21 @@
       <c r="F267" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>45766206</v>
+        <v>45771323</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>From descendants</t>
+          <t>From initial search</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Tricuspid valve stenosis with insufficiency</t>
+          <t>Mitral valve regurgitation due to cardiomyopathy</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12408,27 +8413,12 @@
       <c r="F268" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>45766207</v>
+        <v>45771326</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -12437,7 +8427,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Non-rheumatic mitral valve stenosis with regurgitation</t>
+          <t>Aortic valve regurgitation due to aortic dilation</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12453,27 +8443,12 @@
       <c r="F269" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>45766210</v>
+        <v>45771327</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -12482,7 +8457,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Aortic valve regurgitation due to trauma</t>
+          <t>Mitral valve regurgitation due to acute myocardial infarction with papillary muscle and chordal rupture</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12498,27 +8473,12 @@
       <c r="F270" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>45766211</v>
+        <v>45773080</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -12527,7 +8487,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Aortic valve regurgitation due to dissection</t>
+          <t>Postprocedural mitral valve regurgitation due to papillary muscle and chordal rupture</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12543,831 +8503,6 @@
       <c r="F271" t="inlineStr">
         <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272">
-        <v>45766213</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation due to infiltrative disease</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273">
-        <v>45766214</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation due to acute myocardial infarction without papillary muscle and chordal rupture</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274">
-        <v>45771317</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Prosthetic aortic valve failure requiring replacement</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275">
-        <v>45771321</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Neoaortic valve regurgitation</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276">
-        <v>45771323</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation due to cardiomyopathy</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277">
-        <v>45771326</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Aortic valve regurgitation due to aortic dilation</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278">
-        <v>45771327</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Mitral valve regurgitation due to acute myocardial infarction with papillary muscle and chordal rupture</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279">
-        <v>45773080</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>From initial search</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Postprocedural mitral valve regurgitation due to papillary muscle and chordal rupture</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280">
-        <v>318689</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Syphilitic endocarditis of aortic valve</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281">
-        <v>321107</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Congenital insufficiency of aortic valve</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282">
-        <v>439834</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Rheumatic aortic regurgitation</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283">
-        <v>4108659</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Mitral and aortic incompetence</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284">
-        <v>35622773</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Laubry Pezzi syndrome</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285">
-        <v>42539157</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Endocarditis of neoaortic valve</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286">
-        <v>42597024</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Endocarditis of aortic valve</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>SNOMED Veterinary</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287">
-        <v>42599746</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Physiologic aortic insufficiency</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>SNOMED Veterinary</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288">
-        <v>43020882</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Infective endocarditis of aortic valve</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289">
-        <v>45766095</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>From descendants</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Endocarditis of prosthetic aortic valve</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>SNOMED</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
